--- a/survey_templates/032_food_service_satisfaction_survey--survey_templates.xlsx
+++ b/survey_templates/032_food_service_satisfaction_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -594,7 +594,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>how_satisfy_with_food</t>
+          <t>Question2 Score</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -663,7 +663,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>what_can_improve</t>
+          <t>Question4 Answer</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -755,7 +755,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Question6 Score</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -778,7 +778,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Question6 Answer</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>how_satisfy_with_food</t>
+          <t>Question7 Score</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>what_can_improve</t>
+          <t>Question7 Answer</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>how_satisfy_with_service</t>
+          <t>Question8 Score</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -870,7 +870,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>what_can_improve</t>
+          <t>Question8</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -893,7 +893,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>overall_satisfaction</t>
+          <t>Question9 Score</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>what_can_improve</t>
+          <t>Question9 Answer</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -939,7 +939,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>score</t>
+          <t>Question10 Score</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -962,7 +962,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>comments</t>
+          <t>Question10 Answer</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -983,7 +983,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -1033,131 +1033,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>prophet</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Prophet</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>question_prophets_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>prophet</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Prophet</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
